--- a/output/2026-09-05_02_Italia_Calabria_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-05_02_Italia_Calabria_Componentistica_Ventilazione_industriale.xlsx
@@ -478,7 +478,6 @@
           <t>Alberti Biagio</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Cosenza</t>
@@ -516,7 +515,6 @@
           <t>Due "E" Elettromeccanica di Camposani</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Cosenza</t>
@@ -574,7 +572,6 @@
           <t>0984 466024 / 335 1337585</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Agenzia di rappresentanza climatizzazione/ventilazione dal 1990 (Daikin, Tecnosystemi Group, Zehnder, Faral); riferimento per rivenditori e installatori in Calabria e provincia di Salerno. Email non reperita.</t>
@@ -612,7 +609,6 @@
           <t>0984 402755 / 0984 404240</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Ingrosso/dettaglio materiale elettrico (Contrada Lecco 1, Rende). Stessa azienda con filiale a Vibo Valentia (Viale Affaccio 86, vedi riga dedicata). Gamma specifica ventilazione industriale non pienamente confermata dai motori di ricerca; email non reperita per questa sede.</t>
@@ -650,7 +646,6 @@
           <t>0984 980826</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Produttore (dal 1996) di pannelli preisolati in poliuretano/alluminio e canalizzazioni aerauliche per distribuzione aria (linee Indoor, Outdoor, Health, Praktico). Sede Figline Vegliaturo (CS). Email non reperita.</t>
@@ -730,7 +725,6 @@
           <t>0961 367091 / 0961 753737</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Ingrosso/dettaglio dal 1995: materiali/accessori per elettrico, idraulico, riscaldamento, climatizzazione, ventilazione e aspirazione (in catalogo online ventilatori e aspiratori Vortice). Email non reperita.</t>
@@ -810,7 +804,6 @@
           <t>0962 961556</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Filiale calabrese (sede centrale a Lamezia Terme, altre filiali a Rende e Satriano) di distributore di materiale elettrico e termoidraulico, ingrosso e dettaglio, civile e industriale. Gamma specifica ventilazione non confermata nel dettaglio; email non reperita.</t>
@@ -848,7 +841,6 @@
           <t>+39 0963 255893</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Distribuzione materiali elettrici, illuminotecnica e componenti per impianti/motori; sede in Zona Industriale, Maierato (VV), con sede operativa anche a Vibo Valentia. Gamma specifica ventilazione non confermata nel dettaglio; email non reperita.</t>
@@ -893,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Stessa azienda di "Majorano Calabria S.r.l." con sede a Rende (CS): filiale/punto vendita a Vibo Valentia, indirizzo verificato Viale Affaccio 86 (indirizzo "Via S. Aloe 61" della lista grezza non confermato dalle fonti trovate). Ingrosso/dettaglio materiale elettrico.</t>
+          <t>Stessa azienda di "Majorano Calabria S.r.l." con sede a Rende (CS): filiale/punto vendita a Vibo Valentia, indirizzo verificato Viale Affaccio 86 (indirizzo "Via S. Aloe 61" della lista grezza non confermato dalle fonti trovate). Ingrosso/dettaglio materiale elettrico. [DUPLICATO — vedi anche: 2026-09-05_02_Italia_Calabria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/output/2026-09-05_02_Italia_Calabria_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-05_02_Italia_Calabria_Componentistica_Ventilazione_industriale.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
